--- a/input/detect_ROE_BUY_20180729.xlsx
+++ b/input/detect_ROE_BUY_20180729.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Source\akshare\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D64C7E33-6C58-443D-B445-E98C38F46F0E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E23F959-DF88-4E54-8E48-7E10B5D6EC51}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9012" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -396,7 +396,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -413,6 +413,9 @@
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -716,20 +719,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q45"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" customWidth="1"/>
-    <col min="10" max="10" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="6.6640625" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -745,46 +749,47 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="8"/>
+      <c r="G1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I1">
+      <c r="J1">
         <v>2</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K1">
+      <c r="L1">
         <v>0.3</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="6">
+      <c r="N1" s="6">
         <v>5000000</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O1">
+      <c r="P1">
         <f>COUNTA(A2:A290)</f>
         <v>44</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="6">
-        <f>M1/O1</f>
+      <c r="R1" s="6">
+        <f>N1/P1</f>
         <v>113636.36363636363</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -800,23 +805,24 @@
       <c r="E2" s="2">
         <v>35.07</v>
       </c>
-      <c r="F2">
-        <f>$I$1-E2*($I$1-$K$1)/100</f>
+      <c r="F2" s="2"/>
+      <c r="G2">
+        <f>$J$1-E2*($J$1-$L$1)/100</f>
         <v>1.40381</v>
       </c>
-      <c r="G2" s="7">
-        <f>F2*$Q$1</f>
+      <c r="H2" s="7">
+        <f>G2*$R$1</f>
         <v>159523.86363636362</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="7">
-        <f>SUM(G2:G290)</f>
+      <c r="L2" s="7">
+        <f>SUM(H2:H290)</f>
         <v>7644051.1363636358</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -832,16 +838,17 @@
       <c r="E3" s="2">
         <v>24.04</v>
       </c>
-      <c r="F3">
-        <f t="shared" ref="F3:F45" si="0">$I$1-E3*($I$1-$K$1)/100</f>
+      <c r="F3" s="2"/>
+      <c r="G3">
+        <f t="shared" ref="G3:G45" si="0">$J$1-E3*($J$1-$L$1)/100</f>
         <v>1.5913200000000001</v>
       </c>
-      <c r="G3" s="7">
-        <f t="shared" ref="G3:G45" si="1">F3*$Q$1</f>
+      <c r="H3" s="7">
+        <f t="shared" ref="H3:H45" si="1">G3*$R$1</f>
         <v>180831.81818181818</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -857,16 +864,17 @@
       <c r="E4" s="2">
         <v>24.04</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2"/>
+      <c r="G4">
         <f t="shared" si="0"/>
         <v>1.5913200000000001</v>
       </c>
-      <c r="G4" s="7">
+      <c r="H4" s="7">
         <f t="shared" si="1"/>
         <v>180831.81818181818</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>32</v>
       </c>
@@ -882,16 +890,17 @@
       <c r="E5" s="2">
         <v>24.04</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2"/>
+      <c r="G5">
         <f t="shared" si="0"/>
         <v>1.5913200000000001</v>
       </c>
-      <c r="G5" s="7">
+      <c r="H5" s="7">
         <f t="shared" si="1"/>
         <v>180831.81818181818</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -907,16 +916,17 @@
       <c r="E6" s="2">
         <v>28.14</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2"/>
+      <c r="G6">
         <f t="shared" si="0"/>
         <v>1.52162</v>
       </c>
-      <c r="G6" s="7">
+      <c r="H6" s="7">
         <f t="shared" si="1"/>
         <v>172911.36363636362</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -932,16 +942,17 @@
       <c r="E7" s="2">
         <v>29.33</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2"/>
+      <c r="G7">
         <f t="shared" si="0"/>
         <v>1.50139</v>
       </c>
-      <c r="G7" s="7">
+      <c r="H7" s="7">
         <f t="shared" si="1"/>
         <v>170612.5</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -957,16 +968,17 @@
       <c r="E8" s="2">
         <v>31.19</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2"/>
+      <c r="G8">
         <f t="shared" si="0"/>
         <v>1.46977</v>
       </c>
-      <c r="G8" s="7">
+      <c r="H8" s="7">
         <f t="shared" si="1"/>
         <v>167019.31818181818</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>38</v>
       </c>
@@ -982,16 +994,17 @@
       <c r="E9" s="2">
         <v>30.83</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2"/>
+      <c r="G9">
         <f t="shared" si="0"/>
         <v>1.4758900000000001</v>
       </c>
-      <c r="G9" s="7">
+      <c r="H9" s="7">
         <f t="shared" si="1"/>
         <v>167714.77272727274</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1007,16 +1020,17 @@
       <c r="E10" s="2">
         <v>27.09</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2"/>
+      <c r="G10">
         <f t="shared" si="0"/>
         <v>1.5394700000000001</v>
       </c>
-      <c r="G10" s="7">
+      <c r="H10" s="7">
         <f t="shared" si="1"/>
         <v>174939.77272727274</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1032,16 +1046,17 @@
       <c r="E11" s="2">
         <v>20.49</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2"/>
+      <c r="G11">
         <f t="shared" si="0"/>
         <v>1.65167</v>
       </c>
-      <c r="G11" s="7">
+      <c r="H11" s="7">
         <f t="shared" si="1"/>
         <v>187689.77272727271</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1057,16 +1072,17 @@
       <c r="E12" s="2">
         <v>16.64</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2"/>
+      <c r="G12">
         <f t="shared" si="0"/>
         <v>1.71712</v>
       </c>
-      <c r="G12" s="7">
+      <c r="H12" s="7">
         <f t="shared" si="1"/>
         <v>195127.27272727271</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>46</v>
       </c>
@@ -1082,16 +1098,17 @@
       <c r="E13" s="2">
         <v>17.71</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2"/>
+      <c r="G13">
         <f t="shared" si="0"/>
         <v>1.6989300000000001</v>
       </c>
-      <c r="G13" s="7">
+      <c r="H13" s="7">
         <f t="shared" si="1"/>
         <v>193060.22727272726</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -1107,16 +1124,17 @@
       <c r="E14" s="2">
         <v>35.89</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2"/>
+      <c r="G14">
         <f t="shared" si="0"/>
         <v>1.3898700000000002</v>
       </c>
-      <c r="G14" s="7">
+      <c r="H14" s="7">
         <f t="shared" si="1"/>
         <v>157939.77272727274</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>48</v>
       </c>
@@ -1132,16 +1150,17 @@
       <c r="E15" s="2">
         <v>94.8</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2"/>
+      <c r="G15">
         <f t="shared" si="0"/>
         <v>0.38840000000000008</v>
       </c>
-      <c r="G15" s="7">
+      <c r="H15" s="7">
         <f t="shared" si="1"/>
         <v>44136.363636363647</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>49</v>
       </c>
@@ -1157,16 +1176,17 @@
       <c r="E16" s="2">
         <v>22.12</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2"/>
+      <c r="G16">
         <f t="shared" si="0"/>
         <v>1.6239600000000001</v>
       </c>
-      <c r="G16" s="7">
+      <c r="H16" s="7">
         <f t="shared" si="1"/>
         <v>184540.90909090909</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>50</v>
       </c>
@@ -1182,16 +1202,17 @@
       <c r="E17" s="2">
         <v>5.22</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="2"/>
+      <c r="G17">
         <f t="shared" si="0"/>
         <v>1.91126</v>
       </c>
-      <c r="G17" s="7">
+      <c r="H17" s="7">
         <f t="shared" si="1"/>
         <v>217188.63636363635</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1207,16 +1228,17 @@
       <c r="E18" s="2">
         <v>3.98</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="2"/>
+      <c r="G18">
         <f t="shared" si="0"/>
         <v>1.9323399999999999</v>
       </c>
-      <c r="G18" s="7">
+      <c r="H18" s="7">
         <f t="shared" si="1"/>
         <v>219584.09090909088</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>53</v>
       </c>
@@ -1232,16 +1254,17 @@
       <c r="E19" s="2">
         <v>1.37</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="2"/>
+      <c r="G19">
         <f t="shared" si="0"/>
         <v>1.97671</v>
       </c>
-      <c r="G19" s="7">
+      <c r="H19" s="7">
         <f t="shared" si="1"/>
         <v>224626.13636363635</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -1257,16 +1280,17 @@
       <c r="E20" s="2">
         <v>25.69</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="2"/>
+      <c r="G20">
         <f t="shared" si="0"/>
         <v>1.5632699999999999</v>
       </c>
-      <c r="G20" s="7">
+      <c r="H20" s="7">
         <f t="shared" si="1"/>
         <v>177644.31818181818</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
@@ -1282,16 +1306,17 @@
       <c r="E21" s="2">
         <v>25.69</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="2"/>
+      <c r="G21">
         <f t="shared" si="0"/>
         <v>1.5632699999999999</v>
       </c>
-      <c r="G21" s="7">
+      <c r="H21" s="7">
         <f t="shared" si="1"/>
         <v>177644.31818181818</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -1307,16 +1332,17 @@
       <c r="E22" s="2">
         <v>23.46</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="2"/>
+      <c r="G22">
         <f t="shared" si="0"/>
         <v>1.60118</v>
       </c>
-      <c r="G22" s="7">
+      <c r="H22" s="7">
         <f t="shared" si="1"/>
         <v>181952.27272727274</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>13</v>
       </c>
@@ -1332,16 +1358,17 @@
       <c r="E23" s="2">
         <v>14.7</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="2"/>
+      <c r="G23">
         <f t="shared" si="0"/>
         <v>1.7501</v>
       </c>
-      <c r="G23" s="7">
+      <c r="H23" s="7">
         <f t="shared" si="1"/>
         <v>198875</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>61</v>
       </c>
@@ -1357,16 +1384,17 @@
       <c r="E24" s="2">
         <v>12.76</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="2"/>
+      <c r="G24">
         <f t="shared" si="0"/>
         <v>1.78308</v>
       </c>
-      <c r="G24" s="7">
+      <c r="H24" s="7">
         <f t="shared" si="1"/>
         <v>202622.72727272726</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -1382,16 +1410,17 @@
       <c r="E25" s="2">
         <v>13.03</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="2"/>
+      <c r="G25">
         <f t="shared" si="0"/>
         <v>1.7784900000000001</v>
       </c>
-      <c r="G25" s="7">
+      <c r="H25" s="7">
         <f t="shared" si="1"/>
         <v>202101.13636363638</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1407,16 +1436,17 @@
       <c r="E26" s="2">
         <v>13.7</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="2"/>
+      <c r="G26">
         <f t="shared" si="0"/>
         <v>1.7671000000000001</v>
       </c>
-      <c r="G26" s="7">
+      <c r="H26" s="7">
         <f t="shared" si="1"/>
         <v>200806.81818181818</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>11</v>
       </c>
@@ -1432,16 +1462,17 @@
       <c r="E27" s="2">
         <v>19.920000000000002</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="2"/>
+      <c r="G27">
         <f t="shared" si="0"/>
         <v>1.6613599999999999</v>
       </c>
-      <c r="G27" s="7">
+      <c r="H27" s="7">
         <f t="shared" si="1"/>
         <v>188790.90909090909</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1457,16 +1488,17 @@
       <c r="E28" s="2">
         <v>20.27</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="2"/>
+      <c r="G28">
         <f t="shared" si="0"/>
         <v>1.65541</v>
       </c>
-      <c r="G28" s="7">
+      <c r="H28" s="7">
         <f t="shared" si="1"/>
         <v>188114.77272727274</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1482,16 +1514,17 @@
       <c r="E29" s="2">
         <v>12.23</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="2"/>
+      <c r="G29">
         <f t="shared" si="0"/>
         <v>1.79209</v>
       </c>
-      <c r="G29" s="7">
+      <c r="H29" s="7">
         <f t="shared" si="1"/>
         <v>203646.59090909091</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1507,16 +1540,17 @@
       <c r="E30" s="2">
         <v>10.43</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="2"/>
+      <c r="G30">
         <f t="shared" si="0"/>
         <v>1.8226900000000001</v>
       </c>
-      <c r="G30" s="7">
+      <c r="H30" s="7">
         <f t="shared" si="1"/>
         <v>207123.86363636365</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -1532,16 +1566,17 @@
       <c r="E31" s="2">
         <v>8.9</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="2"/>
+      <c r="G31">
         <f t="shared" si="0"/>
         <v>1.8487</v>
       </c>
-      <c r="G31" s="7">
+      <c r="H31" s="7">
         <f t="shared" si="1"/>
         <v>210079.54545454544</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -1557,16 +1592,17 @@
       <c r="E32" s="2">
         <v>12.47</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="2"/>
+      <c r="G32">
         <f t="shared" si="0"/>
         <v>1.7880099999999999</v>
       </c>
-      <c r="G32" s="7">
+      <c r="H32" s="7">
         <f t="shared" si="1"/>
         <v>203182.95454545453</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -1582,16 +1618,17 @@
       <c r="E33" s="2">
         <v>13.6</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="2"/>
+      <c r="G33">
         <f t="shared" si="0"/>
         <v>1.7688000000000001</v>
       </c>
-      <c r="G33" s="7">
+      <c r="H33" s="7">
         <f t="shared" si="1"/>
         <v>201000</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -1607,16 +1644,17 @@
       <c r="E34" s="2">
         <v>13.72</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="2"/>
+      <c r="G34">
         <f t="shared" si="0"/>
         <v>1.7667600000000001</v>
       </c>
-      <c r="G34" s="7">
+      <c r="H34" s="7">
         <f t="shared" si="1"/>
         <v>200768.18181818182</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>77</v>
       </c>
@@ -1632,16 +1670,17 @@
       <c r="E35" s="2">
         <v>11.66</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="2"/>
+      <c r="G35">
         <f t="shared" si="0"/>
         <v>1.8017799999999999</v>
       </c>
-      <c r="G35" s="7">
+      <c r="H35" s="7">
         <f t="shared" si="1"/>
         <v>204747.72727272726</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>8</v>
       </c>
@@ -1657,16 +1696,17 @@
       <c r="E36" s="2">
         <v>9.0399999999999991</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="2"/>
+      <c r="G36">
         <f t="shared" si="0"/>
         <v>1.84632</v>
       </c>
-      <c r="G36" s="7">
+      <c r="H36" s="7">
         <f t="shared" si="1"/>
         <v>209809.09090909091</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -1682,16 +1722,17 @@
       <c r="E37" s="2">
         <v>1.23</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="2"/>
+      <c r="G37">
         <f t="shared" si="0"/>
         <v>1.97909</v>
       </c>
-      <c r="G37" s="7">
+      <c r="H37" s="7">
         <f t="shared" si="1"/>
         <v>224896.59090909091</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>80</v>
       </c>
@@ -1707,16 +1748,17 @@
       <c r="E38" s="2">
         <v>60.74</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="2"/>
+      <c r="G38">
         <f t="shared" si="0"/>
         <v>0.96741999999999995</v>
       </c>
-      <c r="G38" s="7">
+      <c r="H38" s="7">
         <f t="shared" si="1"/>
         <v>109934.0909090909</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -1732,16 +1774,17 @@
       <c r="E39" s="2">
         <v>62.31</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="2"/>
+      <c r="G39">
         <f t="shared" si="0"/>
         <v>0.94072999999999984</v>
       </c>
-      <c r="G39" s="7">
+      <c r="H39" s="7">
         <f t="shared" si="1"/>
         <v>106901.13636363634</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>6</v>
       </c>
@@ -1757,16 +1800,17 @@
       <c r="E40" s="2">
         <v>58.98</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="2"/>
+      <c r="G40">
         <f t="shared" si="0"/>
         <v>0.99734000000000012</v>
       </c>
-      <c r="G40" s="7">
+      <c r="H40" s="7">
         <f t="shared" si="1"/>
         <v>113334.09090909091</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>83</v>
       </c>
@@ -1782,16 +1826,17 @@
       <c r="E41" s="2">
         <v>58.05</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="2"/>
+      <c r="G41">
         <f t="shared" si="0"/>
         <v>1.01315</v>
       </c>
-      <c r="G41" s="7">
+      <c r="H41" s="7">
         <f t="shared" si="1"/>
         <v>115130.68181818181</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>85</v>
       </c>
@@ -1807,16 +1852,17 @@
       <c r="E42" s="2">
         <v>69.19</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="2"/>
+      <c r="G42">
         <f t="shared" si="0"/>
         <v>0.82377000000000011</v>
       </c>
-      <c r="G42" s="7">
+      <c r="H42" s="7">
         <f t="shared" si="1"/>
         <v>93610.227272727279</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>86</v>
       </c>
@@ -1832,16 +1878,17 @@
       <c r="E43" s="2">
         <v>71.739999999999995</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="2"/>
+      <c r="G43">
         <f t="shared" si="0"/>
         <v>0.78042000000000011</v>
       </c>
-      <c r="G43" s="7">
+      <c r="H43" s="7">
         <f t="shared" si="1"/>
         <v>88684.090909090912</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -1857,16 +1904,17 @@
       <c r="E44" s="2">
         <v>53.16</v>
       </c>
-      <c r="F44">
+      <c r="F44" s="2"/>
+      <c r="G44">
         <f t="shared" si="0"/>
         <v>1.0962800000000001</v>
       </c>
-      <c r="G44" s="7">
+      <c r="H44" s="7">
         <f t="shared" si="1"/>
         <v>124577.27272727274</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -1882,11 +1930,12 @@
       <c r="E45" s="2">
         <v>50.89</v>
       </c>
-      <c r="F45">
+      <c r="F45" s="2"/>
+      <c r="G45">
         <f t="shared" si="0"/>
         <v>1.1348699999999998</v>
       </c>
-      <c r="G45" s="7">
+      <c r="H45" s="7">
         <f t="shared" si="1"/>
         <v>128962.49999999997</v>
       </c>
